--- a/data/trans_orig/P21D1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención médica en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49337</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80166</t>
+          <t>81097</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38231</t>
+          <t>38072</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60207</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>93022</t>
+          <t>92562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>131851</t>
+          <t>133150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171551</t>
+          <t>171320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>207270</t>
+          <t>205713</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>235688</t>
+          <t>236774</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>258337</t>
+          <t>259558</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414576</t>
+          <t>414754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>457498</t>
+          <t>457438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27616</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>760</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>10150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>40549</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187242</t>
+          <t>187229</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67422</t>
+          <t>65815</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96204</t>
+          <t>95175</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>95610</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258950</t>
+          <t>258127</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>463109</t>
+          <t>461317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>616989</t>
+          <t>615706</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>333332</t>
+          <t>334444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>364976</t>
+          <t>365838</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,51%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>819060</t>
+          <t>819937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1003160</t>
+          <t>1001289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,55%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12975</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,82 +1540,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>16530</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9960</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>25760</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>21754</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>9359</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>32631</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>16530</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>10357</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>25308</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>21754</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>10131</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>34009</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1638,97 +1638,97 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="R12" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43285</t>
+          <t>43868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>82025</t>
+          <t>81850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>39657</t>
+          <t>36844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68918</t>
+          <t>67028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89780</t>
+          <t>89071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136729</t>
+          <t>137093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>244970</t>
+          <t>245260</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>284067</t>
+          <t>283046</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>253851</t>
+          <t>254651</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>284102</t>
+          <t>285695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>513301</t>
+          <t>512959</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>560775</t>
+          <t>561559</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,06%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2402</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11844</t>
+          <t>11587</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4886</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>16791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98942</t>
+          <t>97017</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>142121</t>
+          <t>140324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104640</t>
+          <t>104884</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>319149</t>
+          <t>287137</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>222699</t>
+          <t>222479</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>427991</t>
+          <t>453992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>49,03%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259899</t>
+          <t>261887</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>304619</t>
+          <t>305179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194143</t>
+          <t>226359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>405632</t>
+          <t>406262</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>488712</t>
+          <t>462561</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>688357</t>
+          <t>688413</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11258</t>
+          <t>11206</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6970</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22033</t>
+          <t>22900</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -2776,97 +2776,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3522</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>219253</t>
+          <t>215490</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>433588</t>
+          <t>430323</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>276550</t>
+          <t>277201</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>535091</t>
+          <t>535322</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>566544</t>
+          <t>569493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>871893</t>
+          <t>879865</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1199514</t>
+          <t>1200333</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1435166</t>
+          <t>1422602</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1027660</t>
+          <t>1032877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1283586</t>
+          <t>1283367</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2331560</t>
+          <t>2317847</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2642692</t>
+          <t>2635653</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,57%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,9%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15095</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45098</t>
+          <t>45395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22945</t>
+          <t>22932</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>42813</t>
+          <t>45318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>81024</t>
+          <t>79425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -3345,97 +3345,97 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="R27" s="2" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>5358</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>5380</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>63652</t>
+          <t>73567</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48564</t>
+          <t>56373</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81097</t>
+          <t>92158</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>47786</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38072</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59327</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>111438</t>
+          <t>128891</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92562</t>
+          <t>109003</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>133150</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>190048</t>
+          <t>200437</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171320</t>
+          <t>180534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205713</t>
+          <t>220251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>248352</t>
+          <t>265521</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>236774</t>
+          <t>251324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>259558</t>
+          <t>278163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>438400</t>
+          <t>465958</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>414754</t>
+          <t>438212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>457438</t>
+          <t>487625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26004</t>
+          <t>28464</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3149</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>836</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10150</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>16048</t>
+          <t>17434</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>8630</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>33294</t>
+          <t>33503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>112527</t>
+          <t>139281</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>40549</t>
+          <t>117762</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187229</t>
+          <t>162606</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>80136</t>
+          <t>91850</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65815</t>
+          <t>75554</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>95175</t>
+          <t>108850</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>192663</t>
+          <t>231130</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95610</t>
+          <t>205637</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>258127</t>
+          <t>261380</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>26,85%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>540638</t>
+          <t>324223</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>461317</t>
+          <t>300233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>615706</t>
+          <t>346255</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>350689</t>
+          <t>393431</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>334444</t>
+          <t>376510</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>365838</t>
+          <t>411205</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>891327</t>
+          <t>717653</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>819937</t>
+          <t>686312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1001289</t>
+          <t>744140</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>6705</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16530</t>
+          <t>18113</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9960</t>
+          <t>11273</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25760</t>
+          <t>27319</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>21754</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9359</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32631</t>
+          <t>35666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60400</t>
+          <t>73100</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>54891</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81850</t>
+          <t>96847</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>51135</t>
+          <t>55626</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36844</t>
+          <t>43198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>67028</t>
+          <t>73136</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>111535</t>
+          <t>128726</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>89071</t>
+          <t>103151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>137093</t>
+          <t>155728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>267352</t>
+          <t>300194</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>245260</t>
+          <t>276393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>283046</t>
+          <t>318578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>271559</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>254651</t>
+          <t>297524</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>285695</t>
+          <t>328057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>538910</t>
+          <t>616255</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>512959</t>
+          <t>589836</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>561559</t>
+          <t>641983</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11587</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>16301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>118566</t>
+          <t>133481</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97017</t>
+          <t>113544</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>140324</t>
+          <t>155491</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>165066</t>
+          <t>110165</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104884</t>
+          <t>92224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>287137</t>
+          <t>127751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>283632</t>
+          <t>243646</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>222479</t>
+          <t>214355</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>453992</t>
+          <t>274192</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>282854</t>
+          <t>293172</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261887</t>
+          <t>271047</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>305179</t>
+          <t>312881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>346004</t>
+          <t>373416</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226359</t>
+          <t>355351</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>406262</t>
+          <t>391728</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>628859</t>
+          <t>666587</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>462561</t>
+          <t>634629</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>688413</t>
+          <t>696295</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16456</t>
+          <t>16686</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6184</t>
+          <t>6451</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3279</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>12718</t>
+          <t>13157</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6970</t>
+          <t>6853</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22900</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>355145</t>
+          <t>419429</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>215490</t>
+          <t>379801</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>430323</t>
+          <t>462742</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>344124</t>
+          <t>312965</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>277201</t>
+          <t>287162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>535322</t>
+          <t>344682</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>699268</t>
+          <t>732394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>569493</t>
+          <t>680259</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>879865</t>
+          <t>785874</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>24,07%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1280892</t>
+          <t>1118025</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1200333</t>
+          <t>1073216</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1422602</t>
+          <t>1157753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1216604</t>
+          <t>1348428</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1032877</t>
+          <t>1316039</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1283367</t>
+          <t>1377198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2497496</t>
+          <t>2466454</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2317847</t>
+          <t>2414253</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2635653</t>
+          <t>2517654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>27741</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>15095</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>45395</t>
+          <t>49705</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31847</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>22932</t>
+          <t>24649</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45318</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>59588</t>
+          <t>64911</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>50519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>86728</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
